--- a/data/sources/BOM_신규_헤드램프_HL22.xlsx
+++ b/data/sources/BOM_신규_헤드램프_HL22.xlsx
@@ -496,7 +496,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="str">
-        <v>PC+ABS</v>
+        <v>PC</v>
       </c>
     </row>
     <row r="6">
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>EPDM</v>
+        <v>실리콘</v>
       </c>
     </row>
   </sheetData>
